--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_projets.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_projets.xlsx
@@ -10,7 +10,6 @@
   <sheets>
     <sheet name="Projet" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Recolteur&amp;Instrument_projet" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Membre_groupe_recolte" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,12 +21,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="57">
-  <si>
-    <t xml:space="preserve">id_projet  (si utilisé ailleurs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nom_responsable</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="53">
+  <si>
+    <t xml:space="preserve">nom_projet</t>
   </si>
   <si>
     <t xml:space="preserve">email_responsable</t>
@@ -39,13 +35,13 @@
     <t xml:space="preserve">date_fin</t>
   </si>
   <si>
-    <t xml:space="preserve">John Doeuf</t>
+    <t xml:space="preserve">test1</t>
   </si>
   <si>
     <t xml:space="preserve">john.doeuf@umontpellier.fr</t>
   </si>
   <si>
-    <t xml:space="preserve">Marine Zwicke</t>
+    <t xml:space="preserve">EcoForUM</t>
   </si>
   <si>
     <t xml:space="preserve">marine.zwicke@umontpellier.fr</t>
@@ -54,9 +50,6 @@
     <t xml:space="preserve">id_instrument/personne</t>
   </si>
   <si>
-    <t xml:space="preserve">id_projet</t>
-  </si>
-  <si>
     <t xml:space="preserve">Instrument/Recolteur (I/R)</t>
   </si>
   <si>
@@ -187,12 +180,6 @@
   </si>
   <si>
     <t xml:space="preserve">Dendro_92261195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_groupe_recolte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id_recolteur</t>
   </si>
 </sst>
 </file>
@@ -203,7 +190,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -228,23 +215,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -289,7 +270,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -311,10 +292,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -507,19 +484,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -528,46 +505,37 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
+      <c r="C2" s="4" t="n">
+        <v>45761</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>45761</v>
-      </c>
-      <c r="E2" s="4" t="n">
         <v>46169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
+      <c r="A3" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="C3" s="4" t="n">
         <v>45352</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="john.doeuf@umontpellier.fr"/>
-    <hyperlink ref="C3" r:id="rId2" display="marine.zwicke@umontpellier.fr"/>
+    <hyperlink ref="B2" r:id="rId1" display="john.doeuf@umontpellier.fr"/>
+    <hyperlink ref="B3" r:id="rId2" display="marine.zwicke@umontpellier.fr"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -585,483 +553,483 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>2</v>
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>2</v>
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>2</v>
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>2</v>
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>2</v>
+        <v>33</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>2</v>
+        <v>34</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>2</v>
+        <v>36</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>2</v>
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>2</v>
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>2</v>
+        <v>39</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>2</v>
+        <v>41</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>2</v>
+        <v>43</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>2</v>
+        <v>44</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>2</v>
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>2</v>
+        <v>46</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>2</v>
+        <v>47</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>2</v>
+        <v>48</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>2</v>
+        <v>49</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>2</v>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1076,47 +1044,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.21"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="guy.tare@etu.umontpellier.fr"/>
-  </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/Base_de_donnees/Fichiers_metadonnees/Metadonnees_projets.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/Metadonnees_projets.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Projet" sheetId="1" state="visible" r:id="rId3"/>
@@ -489,7 +489,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
